--- a/DESIGN.xlsx
+++ b/DESIGN.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="6">
   <si>
     <t>模块类型#朝向</t>
   </si>
@@ -40,6 +40,12 @@
   </si>
   <si>
     <t>往→移动产生升力</t>
+  </si>
+  <si>
+    <t>###THRUSTER#↓</t>
+  </si>
+  <si>
+    <t>###HULL</t>
   </si>
 </sst>
 </file>
@@ -1227,9 +1233,75 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
-  <sheetData/>
+  <dimension ref="B2:B14"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="1"/>
+  <sheetData>
+    <row r="2" spans="2:2">
+      <c r="B2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="2:2">
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="2:2">
+      <c r="B4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="2:2">
+      <c r="B5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="2:2">
+      <c r="B6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="2:2">
+      <c r="B7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="2:2">
+      <c r="B8" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="2:2">
+      <c r="B9" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="2:2">
+      <c r="B10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="2:2">
+      <c r="B11" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="2:2">
+      <c r="B12" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="2:2">
+      <c r="B13" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="2:2">
+      <c r="B14" t="s">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>

--- a/DESIGN.xlsx
+++ b/DESIGN.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="6">
   <si>
     <t>模块类型#朝向</t>
   </si>
@@ -42,10 +42,10 @@
     <t>往→移动产生升力</t>
   </si>
   <si>
-    <t>###THRUSTER#↓</t>
+    <t>###HULL</t>
   </si>
   <si>
-    <t>###HULL</t>
+    <t>###THRUSTER#→</t>
   </si>
 </sst>
 </file>
@@ -1233,72 +1233,23 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="B2:B14"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="1"/>
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="1"/>
   <sheetData>
-    <row r="2" spans="2:2">
-      <c r="B2" t="s">
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="2:2">
-      <c r="B3" t="s">
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
         <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="2:2">
-      <c r="B4" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="2:2">
-      <c r="B5" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="2:2">
-      <c r="B6" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="2:2">
-      <c r="B7" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="2:2">
-      <c r="B8" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="2:2">
-      <c r="B9" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="2:2">
-      <c r="B10" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="2:2">
-      <c r="B11" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="2:2">
-      <c r="B12" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="2:2">
-      <c r="B13" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="2:2">
-      <c r="B14" t="s">
-        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/DESIGN.xlsx
+++ b/DESIGN.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="6">
   <si>
     <t>模块类型#朝向</t>
   </si>
@@ -218,12 +218,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -544,7 +550,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -568,16 +574,16 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -586,90 +592,93 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
@@ -1203,24 +1212,24 @@
   <dimension ref="B2:C4"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="8.4" outlineLevelRow="3" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="16384" width="8.88888888888889" style="1"/>
+    <col min="1" max="16384" width="8.88888888888889" style="2"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:2">
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="2:2">
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="2:3">
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="2" t="s">
         <v>3</v>
       </c>
     </row>
@@ -1233,22 +1242,103 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="1"/>
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="7" outlineLevelCol="4"/>
   <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B1" t="s">
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
-      <c r="A2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" t="s">
+    <row r="2" spans="1:5">
+      <c r="A2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3"/>
+      <c r="E3" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4"/>
+      <c r="E4" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5"/>
+      <c r="C5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>5</v>
       </c>
     </row>

--- a/DESIGN.xlsx
+++ b/DESIGN.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="8">
   <si>
     <t>模块类型#朝向</t>
   </si>
@@ -42,10 +42,16 @@
     <t>往→移动产生升力</t>
   </si>
   <si>
+    <t>###SLOPE#↖</t>
+  </si>
+  <si>
     <t>###HULL</t>
   </si>
   <si>
-    <t>###THRUSTER#→</t>
+    <t>###SLOPE#↗</t>
+  </si>
+  <si>
+    <t>###THRUSTER#↑</t>
   </si>
 </sst>
 </file>
@@ -218,18 +224,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -550,7 +550,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -574,16 +574,16 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -592,93 +592,90 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
@@ -1212,24 +1209,24 @@
   <dimension ref="B2:C4"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="8.4" outlineLevelRow="3" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="16384" width="8.88888888888889" style="2"/>
+    <col min="1" max="16384" width="8.88888888888889" style="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:2">
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="2:2">
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="2:3">
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="1" t="s">
         <v>3</v>
       </c>
     </row>
@@ -1242,104 +1239,40 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E8"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="7" outlineLevelCol="4"/>
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="2" outlineLevelCol="2"/>
   <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:3">
+      <c r="A1" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" t="s">
         <v>4</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D3"/>
-      <c r="E3" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D4"/>
-      <c r="E4" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5"/>
-      <c r="C5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1">
-      <c r="A7" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/DESIGN.xlsx
+++ b/DESIGN.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="11">
   <si>
     <t>模块类型#朝向</t>
   </si>
@@ -52,6 +52,15 @@
   </si>
   <si>
     <t>###THRUSTER#↑</t>
+  </si>
+  <si>
+    <t>###SLOPE#↙</t>
+  </si>
+  <si>
+    <t>###SLOPE#↘</t>
+  </si>
+  <si>
+    <t>###THRUSTER#→</t>
   </si>
 </sst>
 </file>
@@ -1206,8 +1215,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="B2:C4"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="8.4" outlineLevelRow="3" outlineLevelCol="2"/>
+  <dimension ref="B2:D7"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="8.4" outlineLevelRow="6" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="16384" width="8.88888888888889" style="1"/>
   </cols>
@@ -1228,6 +1237,39 @@
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
+      </c>
+    </row>
+    <row r="5" ht="14.4" spans="2:4">
+      <c r="B5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" ht="14.4" spans="2:4">
+      <c r="B6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" ht="14.4" spans="2:4">
+      <c r="B7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D7" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1239,40 +1281,70 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="2" outlineLevelCol="2"/>
+  <dimension ref="A1:J3"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="2"/>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C2" t="s">
         <v>5</v>
       </c>
+      <c r="D2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I2" t="s">
+        <v>6</v>
+      </c>
     </row>
-    <row r="3" spans="1:3">
-      <c r="A3" t="s">
-        <v>4</v>
-      </c>
+    <row r="3" spans="2:10">
       <c r="B3" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="D3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J3" t="s">
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/DESIGN.xlsx
+++ b/DESIGN.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="10">
   <si>
     <t>模块类型#朝向</t>
   </si>
@@ -58,9 +58,6 @@
   </si>
   <si>
     <t>###SLOPE#↘</t>
-  </si>
-  <si>
-    <t>###THRUSTER#→</t>
   </si>
 </sst>
 </file>
@@ -1281,70 +1278,160 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J3"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="2"/>
+  <dimension ref="A1:G5"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="4" outlineLevelCol="6"/>
+  <cols>
+    <col min="1" max="7" width="18.6666666666667" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" t="s">
-        <v>6</v>
+    <row r="1" spans="1:7">
+      <c r="A1" t="str">
+        <f t="shared" ref="A1:G1" si="0">_xlfn.CONCAT("###CS#↗#5#7#",ROW(),"#",COLUMN())</f>
+        <v>###CS#↗#5#7#1#1</v>
+      </c>
+      <c r="B1" t="str">
+        <f t="shared" si="0"/>
+        <v>###CS#↗#5#7#1#2</v>
+      </c>
+      <c r="C1" t="str">
+        <f t="shared" si="0"/>
+        <v>###CS#↗#5#7#1#3</v>
+      </c>
+      <c r="D1" t="str">
+        <f t="shared" si="0"/>
+        <v>###CS#↗#5#7#1#4</v>
+      </c>
+      <c r="E1" t="str">
+        <f t="shared" si="0"/>
+        <v>###CS#↗#5#7#1#5</v>
+      </c>
+      <c r="F1" t="str">
+        <f t="shared" si="0"/>
+        <v>###CS#↗#5#7#1#6</v>
+      </c>
+      <c r="G1" t="str">
+        <f t="shared" si="0"/>
+        <v>###CS#↗#5#7#1#7</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
-      <c r="A2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G2" t="s">
-        <v>5</v>
-      </c>
-      <c r="H2" t="s">
-        <v>5</v>
-      </c>
-      <c r="I2" t="s">
-        <v>6</v>
+    <row r="2" spans="1:7">
+      <c r="A2" t="str">
+        <f t="shared" ref="A2:G2" si="1">_xlfn.CONCAT("###CS#↗#5#7#",ROW(),"#",COLUMN())</f>
+        <v>###CS#↗#5#7#2#1</v>
+      </c>
+      <c r="B2" t="str">
+        <f t="shared" si="1"/>
+        <v>###CS#↗#5#7#2#2</v>
+      </c>
+      <c r="C2" t="str">
+        <f t="shared" si="1"/>
+        <v>###CS#↗#5#7#2#3</v>
+      </c>
+      <c r="D2" t="str">
+        <f t="shared" si="1"/>
+        <v>###CS#↗#5#7#2#4</v>
+      </c>
+      <c r="E2" t="str">
+        <f t="shared" si="1"/>
+        <v>###CS#↗#5#7#2#5</v>
+      </c>
+      <c r="F2" t="str">
+        <f t="shared" si="1"/>
+        <v>###CS#↗#5#7#2#6</v>
+      </c>
+      <c r="G2" t="str">
+        <f t="shared" si="1"/>
+        <v>###CS#↗#5#7#2#7</v>
       </c>
     </row>
-    <row r="3" spans="2:10">
-      <c r="B3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J3" t="s">
-        <v>6</v>
+    <row r="3" spans="1:7">
+      <c r="A3" t="str">
+        <f t="shared" ref="A3:G3" si="2">_xlfn.CONCAT("###CS#↗#5#7#",ROW(),"#",COLUMN())</f>
+        <v>###CS#↗#5#7#3#1</v>
+      </c>
+      <c r="B3" t="str">
+        <f t="shared" si="2"/>
+        <v>###CS#↗#5#7#3#2</v>
+      </c>
+      <c r="C3" t="str">
+        <f t="shared" si="2"/>
+        <v>###CS#↗#5#7#3#3</v>
+      </c>
+      <c r="D3" t="str">
+        <f t="shared" si="2"/>
+        <v>###CS#↗#5#7#3#4</v>
+      </c>
+      <c r="E3" t="str">
+        <f t="shared" si="2"/>
+        <v>###CS#↗#5#7#3#5</v>
+      </c>
+      <c r="F3" t="str">
+        <f t="shared" si="2"/>
+        <v>###CS#↗#5#7#3#6</v>
+      </c>
+      <c r="G3" t="str">
+        <f t="shared" si="2"/>
+        <v>###CS#↗#5#7#3#7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" t="str">
+        <f t="shared" ref="A4:G4" si="3">_xlfn.CONCAT("###CS#↗#5#7#",ROW(),"#",COLUMN())</f>
+        <v>###CS#↗#5#7#4#1</v>
+      </c>
+      <c r="B4" t="str">
+        <f t="shared" si="3"/>
+        <v>###CS#↗#5#7#4#2</v>
+      </c>
+      <c r="C4" t="str">
+        <f t="shared" si="3"/>
+        <v>###CS#↗#5#7#4#3</v>
+      </c>
+      <c r="D4" t="str">
+        <f t="shared" si="3"/>
+        <v>###CS#↗#5#7#4#4</v>
+      </c>
+      <c r="E4" t="str">
+        <f t="shared" si="3"/>
+        <v>###CS#↗#5#7#4#5</v>
+      </c>
+      <c r="F4" t="str">
+        <f t="shared" si="3"/>
+        <v>###CS#↗#5#7#4#6</v>
+      </c>
+      <c r="G4" t="str">
+        <f t="shared" si="3"/>
+        <v>###CS#↗#5#7#4#7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" t="str">
+        <f t="shared" ref="A5:G5" si="4">_xlfn.CONCAT("###CS#↗#5#7#",ROW(),"#",COLUMN())</f>
+        <v>###CS#↗#5#7#5#1</v>
+      </c>
+      <c r="B5" t="str">
+        <f t="shared" si="4"/>
+        <v>###CS#↗#5#7#5#2</v>
+      </c>
+      <c r="C5" t="str">
+        <f t="shared" si="4"/>
+        <v>###CS#↗#5#7#5#3</v>
+      </c>
+      <c r="D5" t="str">
+        <f t="shared" si="4"/>
+        <v>###CS#↗#5#7#5#4</v>
+      </c>
+      <c r="E5" t="str">
+        <f t="shared" si="4"/>
+        <v>###CS#↗#5#7#5#5</v>
+      </c>
+      <c r="F5" t="str">
+        <f t="shared" si="4"/>
+        <v>###CS#↗#5#7#5#6</v>
+      </c>
+      <c r="G5" t="str">
+        <f t="shared" si="4"/>
+        <v>###CS#↗#5#7#5#7</v>
       </c>
     </row>
   </sheetData>

--- a/DESIGN.xlsx
+++ b/DESIGN.xlsx
@@ -1278,160 +1278,149 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G5"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="4" outlineLevelCol="6"/>
+  <dimension ref="A1:K3"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="2"/>
   <cols>
-    <col min="1" max="7" width="18.6666666666667" customWidth="1"/>
+    <col min="1" max="9" width="19.7777777777778" customWidth="1"/>
+    <col min="10" max="11" width="20.8888888888889" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:11">
       <c r="A1" t="str">
-        <f t="shared" ref="A1:G1" si="0">_xlfn.CONCAT("###CS#↗#5#7#",ROW(),"#",COLUMN())</f>
-        <v>###CS#↗#5#7#1#1</v>
+        <f t="shared" ref="A1:K1" si="0">_xlfn.CONCAT("###CS#↗#3#11#",ROW(),"#",COLUMN())</f>
+        <v>###CS#↗#3#11#1#1</v>
       </c>
       <c r="B1" t="str">
         <f t="shared" si="0"/>
-        <v>###CS#↗#5#7#1#2</v>
+        <v>###CS#↗#3#11#1#2</v>
       </c>
       <c r="C1" t="str">
         <f t="shared" si="0"/>
-        <v>###CS#↗#5#7#1#3</v>
+        <v>###CS#↗#3#11#1#3</v>
       </c>
       <c r="D1" t="str">
         <f t="shared" si="0"/>
-        <v>###CS#↗#5#7#1#4</v>
+        <v>###CS#↗#3#11#1#4</v>
       </c>
       <c r="E1" t="str">
         <f t="shared" si="0"/>
-        <v>###CS#↗#5#7#1#5</v>
+        <v>###CS#↗#3#11#1#5</v>
       </c>
       <c r="F1" t="str">
         <f t="shared" si="0"/>
-        <v>###CS#↗#5#7#1#6</v>
+        <v>###CS#↗#3#11#1#6</v>
       </c>
       <c r="G1" t="str">
         <f t="shared" si="0"/>
-        <v>###CS#↗#5#7#1#7</v>
+        <v>###CS#↗#3#11#1#7</v>
+      </c>
+      <c r="H1" t="str">
+        <f t="shared" si="0"/>
+        <v>###CS#↗#3#11#1#8</v>
+      </c>
+      <c r="I1" t="str">
+        <f t="shared" si="0"/>
+        <v>###CS#↗#3#11#1#9</v>
+      </c>
+      <c r="J1" t="str">
+        <f t="shared" si="0"/>
+        <v>###CS#↗#3#11#1#10</v>
+      </c>
+      <c r="K1" t="str">
+        <f t="shared" si="0"/>
+        <v>###CS#↗#3#11#1#11</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:11">
       <c r="A2" t="str">
-        <f t="shared" ref="A2:G2" si="1">_xlfn.CONCAT("###CS#↗#5#7#",ROW(),"#",COLUMN())</f>
-        <v>###CS#↗#5#7#2#1</v>
+        <f t="shared" ref="A2:K2" si="1">_xlfn.CONCAT("###CS#↗#3#11#",ROW(),"#",COLUMN())</f>
+        <v>###CS#↗#3#11#2#1</v>
       </c>
       <c r="B2" t="str">
         <f t="shared" si="1"/>
-        <v>###CS#↗#5#7#2#2</v>
+        <v>###CS#↗#3#11#2#2</v>
       </c>
       <c r="C2" t="str">
         <f t="shared" si="1"/>
-        <v>###CS#↗#5#7#2#3</v>
+        <v>###CS#↗#3#11#2#3</v>
       </c>
       <c r="D2" t="str">
         <f t="shared" si="1"/>
-        <v>###CS#↗#5#7#2#4</v>
+        <v>###CS#↗#3#11#2#4</v>
       </c>
       <c r="E2" t="str">
         <f t="shared" si="1"/>
-        <v>###CS#↗#5#7#2#5</v>
+        <v>###CS#↗#3#11#2#5</v>
       </c>
       <c r="F2" t="str">
         <f t="shared" si="1"/>
-        <v>###CS#↗#5#7#2#6</v>
+        <v>###CS#↗#3#11#2#6</v>
       </c>
       <c r="G2" t="str">
         <f t="shared" si="1"/>
-        <v>###CS#↗#5#7#2#7</v>
+        <v>###CS#↗#3#11#2#7</v>
+      </c>
+      <c r="H2" t="str">
+        <f t="shared" si="1"/>
+        <v>###CS#↗#3#11#2#8</v>
+      </c>
+      <c r="I2" t="str">
+        <f t="shared" si="1"/>
+        <v>###CS#↗#3#11#2#9</v>
+      </c>
+      <c r="J2" t="str">
+        <f t="shared" si="1"/>
+        <v>###CS#↗#3#11#2#10</v>
+      </c>
+      <c r="K2" t="str">
+        <f t="shared" si="1"/>
+        <v>###CS#↗#3#11#2#11</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:11">
       <c r="A3" t="str">
-        <f t="shared" ref="A3:G3" si="2">_xlfn.CONCAT("###CS#↗#5#7#",ROW(),"#",COLUMN())</f>
-        <v>###CS#↗#5#7#3#1</v>
+        <f t="shared" ref="A3:K3" si="2">_xlfn.CONCAT("###CS#↗#3#11#",ROW(),"#",COLUMN())</f>
+        <v>###CS#↗#3#11#3#1</v>
       </c>
       <c r="B3" t="str">
         <f t="shared" si="2"/>
-        <v>###CS#↗#5#7#3#2</v>
+        <v>###CS#↗#3#11#3#2</v>
       </c>
       <c r="C3" t="str">
         <f t="shared" si="2"/>
-        <v>###CS#↗#5#7#3#3</v>
+        <v>###CS#↗#3#11#3#3</v>
       </c>
       <c r="D3" t="str">
         <f t="shared" si="2"/>
-        <v>###CS#↗#5#7#3#4</v>
+        <v>###CS#↗#3#11#3#4</v>
       </c>
       <c r="E3" t="str">
         <f t="shared" si="2"/>
-        <v>###CS#↗#5#7#3#5</v>
+        <v>###CS#↗#3#11#3#5</v>
       </c>
       <c r="F3" t="str">
         <f t="shared" si="2"/>
-        <v>###CS#↗#5#7#3#6</v>
+        <v>###CS#↗#3#11#3#6</v>
       </c>
       <c r="G3" t="str">
         <f t="shared" si="2"/>
-        <v>###CS#↗#5#7#3#7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" t="str">
-        <f t="shared" ref="A4:G4" si="3">_xlfn.CONCAT("###CS#↗#5#7#",ROW(),"#",COLUMN())</f>
-        <v>###CS#↗#5#7#4#1</v>
-      </c>
-      <c r="B4" t="str">
-        <f t="shared" si="3"/>
-        <v>###CS#↗#5#7#4#2</v>
-      </c>
-      <c r="C4" t="str">
-        <f t="shared" si="3"/>
-        <v>###CS#↗#5#7#4#3</v>
-      </c>
-      <c r="D4" t="str">
-        <f t="shared" si="3"/>
-        <v>###CS#↗#5#7#4#4</v>
-      </c>
-      <c r="E4" t="str">
-        <f t="shared" si="3"/>
-        <v>###CS#↗#5#7#4#5</v>
-      </c>
-      <c r="F4" t="str">
-        <f t="shared" si="3"/>
-        <v>###CS#↗#5#7#4#6</v>
-      </c>
-      <c r="G4" t="str">
-        <f t="shared" si="3"/>
-        <v>###CS#↗#5#7#4#7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5" t="str">
-        <f t="shared" ref="A5:G5" si="4">_xlfn.CONCAT("###CS#↗#5#7#",ROW(),"#",COLUMN())</f>
-        <v>###CS#↗#5#7#5#1</v>
-      </c>
-      <c r="B5" t="str">
-        <f t="shared" si="4"/>
-        <v>###CS#↗#5#7#5#2</v>
-      </c>
-      <c r="C5" t="str">
-        <f t="shared" si="4"/>
-        <v>###CS#↗#5#7#5#3</v>
-      </c>
-      <c r="D5" t="str">
-        <f t="shared" si="4"/>
-        <v>###CS#↗#5#7#5#4</v>
-      </c>
-      <c r="E5" t="str">
-        <f t="shared" si="4"/>
-        <v>###CS#↗#5#7#5#5</v>
-      </c>
-      <c r="F5" t="str">
-        <f t="shared" si="4"/>
-        <v>###CS#↗#5#7#5#6</v>
-      </c>
-      <c r="G5" t="str">
-        <f t="shared" si="4"/>
-        <v>###CS#↗#5#7#5#7</v>
+        <v>###CS#↗#3#11#3#7</v>
+      </c>
+      <c r="H3" t="str">
+        <f t="shared" si="2"/>
+        <v>###CS#↗#3#11#3#8</v>
+      </c>
+      <c r="I3" t="str">
+        <f t="shared" si="2"/>
+        <v>###CS#↗#3#11#3#9</v>
+      </c>
+      <c r="J3" t="str">
+        <f t="shared" si="2"/>
+        <v>###CS#↗#3#11#3#10</v>
+      </c>
+      <c r="K3" t="str">
+        <f t="shared" si="2"/>
+        <v>###CS#↗#3#11#3#11</v>
       </c>
     </row>
   </sheetData>

--- a/DESIGN.xlsx
+++ b/DESIGN.xlsx
@@ -1287,140 +1287,140 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" t="str">
-        <f t="shared" ref="A1:K1" si="0">_xlfn.CONCAT("###CS#↗#3#11#",ROW(),"#",COLUMN())</f>
-        <v>###CS#↗#3#11#1#1</v>
+        <f t="shared" ref="A1:K1" si="0">_xlfn.CONCAT("###CS#↘#3#11#",ROW(),"#",COLUMN())</f>
+        <v>###CS#↘#3#11#1#1</v>
       </c>
       <c r="B1" t="str">
         <f t="shared" si="0"/>
-        <v>###CS#↗#3#11#1#2</v>
+        <v>###CS#↘#3#11#1#2</v>
       </c>
       <c r="C1" t="str">
         <f t="shared" si="0"/>
-        <v>###CS#↗#3#11#1#3</v>
+        <v>###CS#↘#3#11#1#3</v>
       </c>
       <c r="D1" t="str">
         <f t="shared" si="0"/>
-        <v>###CS#↗#3#11#1#4</v>
+        <v>###CS#↘#3#11#1#4</v>
       </c>
       <c r="E1" t="str">
         <f t="shared" si="0"/>
-        <v>###CS#↗#3#11#1#5</v>
+        <v>###CS#↘#3#11#1#5</v>
       </c>
       <c r="F1" t="str">
         <f t="shared" si="0"/>
-        <v>###CS#↗#3#11#1#6</v>
+        <v>###CS#↘#3#11#1#6</v>
       </c>
       <c r="G1" t="str">
         <f t="shared" si="0"/>
-        <v>###CS#↗#3#11#1#7</v>
+        <v>###CS#↘#3#11#1#7</v>
       </c>
       <c r="H1" t="str">
         <f t="shared" si="0"/>
-        <v>###CS#↗#3#11#1#8</v>
+        <v>###CS#↘#3#11#1#8</v>
       </c>
       <c r="I1" t="str">
         <f t="shared" si="0"/>
-        <v>###CS#↗#3#11#1#9</v>
+        <v>###CS#↘#3#11#1#9</v>
       </c>
       <c r="J1" t="str">
         <f t="shared" si="0"/>
-        <v>###CS#↗#3#11#1#10</v>
+        <v>###CS#↘#3#11#1#10</v>
       </c>
       <c r="K1" t="str">
         <f t="shared" si="0"/>
-        <v>###CS#↗#3#11#1#11</v>
+        <v>###CS#↘#3#11#1#11</v>
       </c>
     </row>
     <row r="2" spans="1:11">
       <c r="A2" t="str">
-        <f t="shared" ref="A2:K2" si="1">_xlfn.CONCAT("###CS#↗#3#11#",ROW(),"#",COLUMN())</f>
-        <v>###CS#↗#3#11#2#1</v>
+        <f t="shared" ref="A2:K2" si="1">_xlfn.CONCAT("###CS#↘#3#11#",ROW(),"#",COLUMN())</f>
+        <v>###CS#↘#3#11#2#1</v>
       </c>
       <c r="B2" t="str">
         <f t="shared" si="1"/>
-        <v>###CS#↗#3#11#2#2</v>
+        <v>###CS#↘#3#11#2#2</v>
       </c>
       <c r="C2" t="str">
         <f t="shared" si="1"/>
-        <v>###CS#↗#3#11#2#3</v>
+        <v>###CS#↘#3#11#2#3</v>
       </c>
       <c r="D2" t="str">
         <f t="shared" si="1"/>
-        <v>###CS#↗#3#11#2#4</v>
+        <v>###CS#↘#3#11#2#4</v>
       </c>
       <c r="E2" t="str">
         <f t="shared" si="1"/>
-        <v>###CS#↗#3#11#2#5</v>
+        <v>###CS#↘#3#11#2#5</v>
       </c>
       <c r="F2" t="str">
         <f t="shared" si="1"/>
-        <v>###CS#↗#3#11#2#6</v>
+        <v>###CS#↘#3#11#2#6</v>
       </c>
       <c r="G2" t="str">
         <f t="shared" si="1"/>
-        <v>###CS#↗#3#11#2#7</v>
+        <v>###CS#↘#3#11#2#7</v>
       </c>
       <c r="H2" t="str">
         <f t="shared" si="1"/>
-        <v>###CS#↗#3#11#2#8</v>
+        <v>###CS#↘#3#11#2#8</v>
       </c>
       <c r="I2" t="str">
         <f t="shared" si="1"/>
-        <v>###CS#↗#3#11#2#9</v>
+        <v>###CS#↘#3#11#2#9</v>
       </c>
       <c r="J2" t="str">
         <f t="shared" si="1"/>
-        <v>###CS#↗#3#11#2#10</v>
+        <v>###CS#↘#3#11#2#10</v>
       </c>
       <c r="K2" t="str">
         <f t="shared" si="1"/>
-        <v>###CS#↗#3#11#2#11</v>
+        <v>###CS#↘#3#11#2#11</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" t="str">
-        <f t="shared" ref="A3:K3" si="2">_xlfn.CONCAT("###CS#↗#3#11#",ROW(),"#",COLUMN())</f>
-        <v>###CS#↗#3#11#3#1</v>
+        <f t="shared" ref="A3:K3" si="2">_xlfn.CONCAT("###CS#↘#3#11#",ROW(),"#",COLUMN())</f>
+        <v>###CS#↘#3#11#3#1</v>
       </c>
       <c r="B3" t="str">
         <f t="shared" si="2"/>
-        <v>###CS#↗#3#11#3#2</v>
+        <v>###CS#↘#3#11#3#2</v>
       </c>
       <c r="C3" t="str">
         <f t="shared" si="2"/>
-        <v>###CS#↗#3#11#3#3</v>
+        <v>###CS#↘#3#11#3#3</v>
       </c>
       <c r="D3" t="str">
         <f t="shared" si="2"/>
-        <v>###CS#↗#3#11#3#4</v>
+        <v>###CS#↘#3#11#3#4</v>
       </c>
       <c r="E3" t="str">
         <f t="shared" si="2"/>
-        <v>###CS#↗#3#11#3#5</v>
+        <v>###CS#↘#3#11#3#5</v>
       </c>
       <c r="F3" t="str">
         <f t="shared" si="2"/>
-        <v>###CS#↗#3#11#3#6</v>
+        <v>###CS#↘#3#11#3#6</v>
       </c>
       <c r="G3" t="str">
         <f t="shared" si="2"/>
-        <v>###CS#↗#3#11#3#7</v>
+        <v>###CS#↘#3#11#3#7</v>
       </c>
       <c r="H3" t="str">
         <f t="shared" si="2"/>
-        <v>###CS#↗#3#11#3#8</v>
+        <v>###CS#↘#3#11#3#8</v>
       </c>
       <c r="I3" t="str">
         <f t="shared" si="2"/>
-        <v>###CS#↗#3#11#3#9</v>
+        <v>###CS#↘#3#11#3#9</v>
       </c>
       <c r="J3" t="str">
         <f t="shared" si="2"/>
-        <v>###CS#↗#3#11#3#10</v>
+        <v>###CS#↘#3#11#3#10</v>
       </c>
       <c r="K3" t="str">
         <f t="shared" si="2"/>
-        <v>###CS#↗#3#11#3#11</v>
+        <v>###CS#↘#3#11#3#11</v>
       </c>
     </row>
   </sheetData>

--- a/DESIGN.xlsx
+++ b/DESIGN.xlsx
@@ -1278,149 +1278,32 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K3"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="2"/>
+  <dimension ref="A1:D1"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="9" width="19.7777777777778" customWidth="1"/>
-    <col min="10" max="11" width="20.8888888888889" customWidth="1"/>
+    <col min="1" max="4" width="18.6666666666667" customWidth="1"/>
+    <col min="5" max="5" width="8.66666666666667" customWidth="1"/>
+    <col min="6" max="9" width="18.6666666666667" customWidth="1"/>
+    <col min="10" max="11" width="19.7777777777778" customWidth="1"/>
+    <col min="12" max="13" width="20.8888888888889" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:4">
       <c r="A1" t="str">
-        <f t="shared" ref="A1:K1" si="0">_xlfn.CONCAT("###CS#↘#3#11#",ROW(),"#",COLUMN())</f>
-        <v>###CS#↘#3#11#1#1</v>
+        <f>_xlfn.CONCAT("###CS#↖#1#4#",ROW(),"#",COLUMN())</f>
+        <v>###CS#↖#1#4#1#1</v>
       </c>
       <c r="B1" t="str">
-        <f t="shared" si="0"/>
-        <v>###CS#↘#3#11#1#2</v>
+        <f>_xlfn.CONCAT("###CS#↖#1#4#",ROW(),"#",COLUMN())</f>
+        <v>###CS#↖#1#4#1#2</v>
       </c>
       <c r="C1" t="str">
-        <f t="shared" si="0"/>
-        <v>###CS#↘#3#11#1#3</v>
+        <f>_xlfn.CONCAT("###CS#↖#1#4#",ROW(),"#",COLUMN())</f>
+        <v>###CS#↖#1#4#1#3</v>
       </c>
       <c r="D1" t="str">
-        <f t="shared" si="0"/>
-        <v>###CS#↘#3#11#1#4</v>
-      </c>
-      <c r="E1" t="str">
-        <f t="shared" si="0"/>
-        <v>###CS#↘#3#11#1#5</v>
-      </c>
-      <c r="F1" t="str">
-        <f t="shared" si="0"/>
-        <v>###CS#↘#3#11#1#6</v>
-      </c>
-      <c r="G1" t="str">
-        <f t="shared" si="0"/>
-        <v>###CS#↘#3#11#1#7</v>
-      </c>
-      <c r="H1" t="str">
-        <f t="shared" si="0"/>
-        <v>###CS#↘#3#11#1#8</v>
-      </c>
-      <c r="I1" t="str">
-        <f t="shared" si="0"/>
-        <v>###CS#↘#3#11#1#9</v>
-      </c>
-      <c r="J1" t="str">
-        <f t="shared" si="0"/>
-        <v>###CS#↘#3#11#1#10</v>
-      </c>
-      <c r="K1" t="str">
-        <f t="shared" si="0"/>
-        <v>###CS#↘#3#11#1#11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11">
-      <c r="A2" t="str">
-        <f t="shared" ref="A2:K2" si="1">_xlfn.CONCAT("###CS#↘#3#11#",ROW(),"#",COLUMN())</f>
-        <v>###CS#↘#3#11#2#1</v>
-      </c>
-      <c r="B2" t="str">
-        <f t="shared" si="1"/>
-        <v>###CS#↘#3#11#2#2</v>
-      </c>
-      <c r="C2" t="str">
-        <f t="shared" si="1"/>
-        <v>###CS#↘#3#11#2#3</v>
-      </c>
-      <c r="D2" t="str">
-        <f t="shared" si="1"/>
-        <v>###CS#↘#3#11#2#4</v>
-      </c>
-      <c r="E2" t="str">
-        <f t="shared" si="1"/>
-        <v>###CS#↘#3#11#2#5</v>
-      </c>
-      <c r="F2" t="str">
-        <f t="shared" si="1"/>
-        <v>###CS#↘#3#11#2#6</v>
-      </c>
-      <c r="G2" t="str">
-        <f t="shared" si="1"/>
-        <v>###CS#↘#3#11#2#7</v>
-      </c>
-      <c r="H2" t="str">
-        <f t="shared" si="1"/>
-        <v>###CS#↘#3#11#2#8</v>
-      </c>
-      <c r="I2" t="str">
-        <f t="shared" si="1"/>
-        <v>###CS#↘#3#11#2#9</v>
-      </c>
-      <c r="J2" t="str">
-        <f t="shared" si="1"/>
-        <v>###CS#↘#3#11#2#10</v>
-      </c>
-      <c r="K2" t="str">
-        <f t="shared" si="1"/>
-        <v>###CS#↘#3#11#2#11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
-      <c r="A3" t="str">
-        <f t="shared" ref="A3:K3" si="2">_xlfn.CONCAT("###CS#↘#3#11#",ROW(),"#",COLUMN())</f>
-        <v>###CS#↘#3#11#3#1</v>
-      </c>
-      <c r="B3" t="str">
-        <f t="shared" si="2"/>
-        <v>###CS#↘#3#11#3#2</v>
-      </c>
-      <c r="C3" t="str">
-        <f t="shared" si="2"/>
-        <v>###CS#↘#3#11#3#3</v>
-      </c>
-      <c r="D3" t="str">
-        <f t="shared" si="2"/>
-        <v>###CS#↘#3#11#3#4</v>
-      </c>
-      <c r="E3" t="str">
-        <f t="shared" si="2"/>
-        <v>###CS#↘#3#11#3#5</v>
-      </c>
-      <c r="F3" t="str">
-        <f t="shared" si="2"/>
-        <v>###CS#↘#3#11#3#6</v>
-      </c>
-      <c r="G3" t="str">
-        <f t="shared" si="2"/>
-        <v>###CS#↘#3#11#3#7</v>
-      </c>
-      <c r="H3" t="str">
-        <f t="shared" si="2"/>
-        <v>###CS#↘#3#11#3#8</v>
-      </c>
-      <c r="I3" t="str">
-        <f t="shared" si="2"/>
-        <v>###CS#↘#3#11#3#9</v>
-      </c>
-      <c r="J3" t="str">
-        <f t="shared" si="2"/>
-        <v>###CS#↘#3#11#3#10</v>
-      </c>
-      <c r="K3" t="str">
-        <f t="shared" si="2"/>
-        <v>###CS#↘#3#11#3#11</v>
+        <f>_xlfn.CONCAT("###CS#↖#1#4#",ROW(),"#",COLUMN())</f>
+        <v>###CS#↖#1#4#1#4</v>
       </c>
     </row>
   </sheetData>

--- a/DESIGN.xlsx
+++ b/DESIGN.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="10">
   <si>
     <t>模块类型#朝向</t>
   </si>
@@ -1278,8 +1278,8 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D1"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="3"/>
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="2" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="4" width="18.6666666666667" customWidth="1"/>
     <col min="5" max="5" width="8.66666666666667" customWidth="1"/>
@@ -1288,22 +1288,14 @@
     <col min="12" max="13" width="20.8888888888889" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" t="str">
-        <f>_xlfn.CONCAT("###CS#↖#1#4#",ROW(),"#",COLUMN())</f>
-        <v>###CS#↖#1#4#1#1</v>
-      </c>
-      <c r="B1" t="str">
-        <f>_xlfn.CONCAT("###CS#↖#1#4#",ROW(),"#",COLUMN())</f>
-        <v>###CS#↖#1#4#1#2</v>
-      </c>
-      <c r="C1" t="str">
-        <f>_xlfn.CONCAT("###CS#↖#1#4#",ROW(),"#",COLUMN())</f>
-        <v>###CS#↖#1#4#1#3</v>
-      </c>
-      <c r="D1" t="str">
-        <f>_xlfn.CONCAT("###CS#↖#1#4#",ROW(),"#",COLUMN())</f>
-        <v>###CS#↖#1#4#1#4</v>
+    <row r="1" spans="1:1">
+      <c r="A1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="2:2">
+      <c r="B3" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/DESIGN.xlsx
+++ b/DESIGN.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="11">
   <si>
     <t>模块类型#朝向</t>
   </si>
@@ -58,6 +58,9 @@
   </si>
   <si>
     <t>###SLOPE#↘</t>
+  </si>
+  <si>
+    <t>PLACEHOLDER</t>
   </si>
 </sst>
 </file>
@@ -1278,8 +1281,8 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="2" outlineLevelCol="1"/>
+  <dimension ref="A1:D33"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="4" width="18.6666666666667" customWidth="1"/>
     <col min="5" max="5" width="8.66666666666667" customWidth="1"/>
@@ -1290,12 +1293,186 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" spans="2:2">
-      <c r="B3" t="s">
+      <c r="C2" t="s">
         <v>5</v>
+      </c>
+      <c r="D2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5"/>
+      <c r="C5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/DESIGN.xlsx
+++ b/DESIGN.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="11">
   <si>
     <t>模块类型#朝向</t>
   </si>
@@ -1281,8 +1281,8 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D33"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="3"/>
+  <dimension ref="A1:J33"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="4" width="18.6666666666667" customWidth="1"/>
     <col min="5" max="5" width="8.66666666666667" customWidth="1"/>
@@ -1310,15 +1310,30 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:1">
+    <row r="3" spans="1:4">
       <c r="A3" t="s">
         <v>10</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
         <v>10</v>
       </c>
+      <c r="B4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" t="s">
+        <v>5</v>
+      </c>
       <c r="D4" t="s">
         <v>5</v>
       </c>
@@ -1327,7 +1342,9 @@
       <c r="A5" t="s">
         <v>10</v>
       </c>
-      <c r="B5"/>
+      <c r="B5" t="s">
+        <v>5</v>
+      </c>
       <c r="C5" t="s">
         <v>5</v>
       </c>
@@ -1350,84 +1367,384 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:1">
+    <row r="9" spans="1:10">
       <c r="A9" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="10" spans="1:1">
+      <c r="B9"/>
+      <c r="E9" t="s">
+        <v>5</v>
+      </c>
+      <c r="F9" t="s">
+        <v>5</v>
+      </c>
+      <c r="G9" t="s">
+        <v>5</v>
+      </c>
+      <c r="H9" t="s">
+        <v>5</v>
+      </c>
+      <c r="I9" t="s">
+        <v>5</v>
+      </c>
+      <c r="J9" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
       <c r="A10" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="11" spans="1:1">
+      <c r="B10"/>
+      <c r="E10" t="s">
+        <v>5</v>
+      </c>
+      <c r="F10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G10" t="s">
+        <v>5</v>
+      </c>
+      <c r="H10" t="s">
+        <v>5</v>
+      </c>
+      <c r="I10" t="s">
+        <v>5</v>
+      </c>
+      <c r="J10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
       <c r="A11" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="12" spans="1:1">
+      <c r="B11"/>
+      <c r="E11" t="s">
+        <v>5</v>
+      </c>
+      <c r="F11" t="s">
+        <v>5</v>
+      </c>
+      <c r="G11" t="s">
+        <v>5</v>
+      </c>
+      <c r="H11" t="s">
+        <v>5</v>
+      </c>
+      <c r="I11" t="s">
+        <v>5</v>
+      </c>
+      <c r="J11" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
       <c r="A12" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="13" spans="1:1">
+      <c r="B12"/>
+      <c r="C12"/>
+      <c r="D12"/>
+      <c r="E12" t="s">
+        <v>5</v>
+      </c>
+      <c r="F12" t="s">
+        <v>5</v>
+      </c>
+      <c r="G12" t="s">
+        <v>5</v>
+      </c>
+      <c r="H12" t="s">
+        <v>5</v>
+      </c>
+      <c r="I12" t="s">
+        <v>5</v>
+      </c>
+      <c r="J12" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
       <c r="A13" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="14" spans="1:1">
+      <c r="B13"/>
+      <c r="C13"/>
+      <c r="D13"/>
+      <c r="E13" t="s">
+        <v>5</v>
+      </c>
+      <c r="F13" t="s">
+        <v>5</v>
+      </c>
+      <c r="G13" t="s">
+        <v>5</v>
+      </c>
+      <c r="H13" t="s">
+        <v>5</v>
+      </c>
+      <c r="I13" t="s">
+        <v>5</v>
+      </c>
+      <c r="J13" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
       <c r="A14" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="15" spans="1:1">
+      <c r="B14"/>
+      <c r="C14"/>
+      <c r="D14"/>
+      <c r="E14" t="s">
+        <v>5</v>
+      </c>
+      <c r="F14" t="s">
+        <v>5</v>
+      </c>
+      <c r="G14" t="s">
+        <v>5</v>
+      </c>
+      <c r="H14" t="s">
+        <v>5</v>
+      </c>
+      <c r="I14" t="s">
+        <v>5</v>
+      </c>
+      <c r="J14" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
       <c r="A15" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="16" spans="1:1">
+      <c r="E15" t="s">
+        <v>5</v>
+      </c>
+      <c r="F15" t="s">
+        <v>5</v>
+      </c>
+      <c r="G15" t="s">
+        <v>5</v>
+      </c>
+      <c r="H15" t="s">
+        <v>5</v>
+      </c>
+      <c r="I15" t="s">
+        <v>5</v>
+      </c>
+      <c r="J15" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
       <c r="A16" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="17" spans="1:1">
+      <c r="E16" t="s">
+        <v>5</v>
+      </c>
+      <c r="F16" t="s">
+        <v>5</v>
+      </c>
+      <c r="G16" t="s">
+        <v>5</v>
+      </c>
+      <c r="H16" t="s">
+        <v>5</v>
+      </c>
+      <c r="I16" t="s">
+        <v>5</v>
+      </c>
+      <c r="J16" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
       <c r="A17" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="18" spans="1:1">
+      <c r="E17" t="s">
+        <v>5</v>
+      </c>
+      <c r="F17" t="s">
+        <v>5</v>
+      </c>
+      <c r="G17" t="s">
+        <v>5</v>
+      </c>
+      <c r="H17" t="s">
+        <v>5</v>
+      </c>
+      <c r="I17" t="s">
+        <v>5</v>
+      </c>
+      <c r="J17" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
       <c r="A18" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="19" spans="1:1">
+      <c r="E18" t="s">
+        <v>5</v>
+      </c>
+      <c r="F18" t="s">
+        <v>5</v>
+      </c>
+      <c r="G18" t="s">
+        <v>5</v>
+      </c>
+      <c r="H18" t="s">
+        <v>5</v>
+      </c>
+      <c r="I18" t="s">
+        <v>5</v>
+      </c>
+      <c r="J18" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
       <c r="A19" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="20" spans="1:1">
+      <c r="E19" t="s">
+        <v>5</v>
+      </c>
+      <c r="F19" t="s">
+        <v>5</v>
+      </c>
+      <c r="G19" t="s">
+        <v>5</v>
+      </c>
+      <c r="H19" t="s">
+        <v>5</v>
+      </c>
+      <c r="I19" t="s">
+        <v>5</v>
+      </c>
+      <c r="J19" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
       <c r="A20" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="21" spans="1:1">
+      <c r="E20" t="s">
+        <v>5</v>
+      </c>
+      <c r="F20" t="s">
+        <v>5</v>
+      </c>
+      <c r="G20" t="s">
+        <v>5</v>
+      </c>
+      <c r="H20" t="s">
+        <v>5</v>
+      </c>
+      <c r="I20" t="s">
+        <v>5</v>
+      </c>
+      <c r="J20" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
       <c r="A21" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="22" spans="1:1">
+      <c r="E21" t="s">
+        <v>5</v>
+      </c>
+      <c r="F21" t="s">
+        <v>5</v>
+      </c>
+      <c r="G21" t="s">
+        <v>5</v>
+      </c>
+      <c r="H21" t="s">
+        <v>5</v>
+      </c>
+      <c r="I21" t="s">
+        <v>5</v>
+      </c>
+      <c r="J21" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
       <c r="A22" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="23" spans="1:1">
+      <c r="E22" t="s">
+        <v>5</v>
+      </c>
+      <c r="F22" t="s">
+        <v>5</v>
+      </c>
+      <c r="G22" t="s">
+        <v>5</v>
+      </c>
+      <c r="H22" t="s">
+        <v>5</v>
+      </c>
+      <c r="I22" t="s">
+        <v>5</v>
+      </c>
+      <c r="J22" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
       <c r="A23" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="24" spans="1:1">
+      <c r="E23" t="s">
+        <v>5</v>
+      </c>
+      <c r="F23" t="s">
+        <v>5</v>
+      </c>
+      <c r="G23" t="s">
+        <v>5</v>
+      </c>
+      <c r="H23" t="s">
+        <v>5</v>
+      </c>
+      <c r="I23" t="s">
+        <v>5</v>
+      </c>
+      <c r="J23" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10">
       <c r="A24" t="s">
         <v>10</v>
+      </c>
+      <c r="E24" t="s">
+        <v>5</v>
+      </c>
+      <c r="F24" t="s">
+        <v>5</v>
+      </c>
+      <c r="G24" t="s">
+        <v>5</v>
+      </c>
+      <c r="H24" t="s">
+        <v>5</v>
+      </c>
+      <c r="I24" t="s">
+        <v>5</v>
+      </c>
+      <c r="J24" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="25" spans="1:1">

--- a/DESIGN.xlsx
+++ b/DESIGN.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="12">
   <si>
     <t>模块类型#朝向</t>
   </si>
@@ -62,6 +62,9 @@
   <si>
     <t>PLACEHOLDER</t>
   </si>
+  <si>
+    <t>JOINT</t>
+  </si>
 </sst>
 </file>
 
@@ -233,12 +236,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -559,7 +568,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -583,16 +592,16 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -601,90 +610,93 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
@@ -1218,24 +1230,24 @@
   <dimension ref="B2:D7"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="8.4" outlineLevelRow="6" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="16384" width="8.88888888888889" style="1"/>
+    <col min="1" max="16384" width="8.88888888888889" style="2"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:2">
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="2:2">
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="2:3">
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="2" t="s">
         <v>3</v>
       </c>
     </row>
@@ -1281,513 +1293,249 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J33"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
+  <dimension ref="A1:H33"/>
+  <sheetFormatPr defaultColWidth="15.7777777777778" defaultRowHeight="14.4" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="4" width="18.6666666666667" customWidth="1"/>
-    <col min="5" max="5" width="8.66666666666667" customWidth="1"/>
-    <col min="6" max="9" width="18.6666666666667" customWidth="1"/>
+    <col min="1" max="9" width="5.77777777777778" customWidth="1"/>
     <col min="10" max="11" width="19.7777777777778" customWidth="1"/>
     <col min="12" max="13" width="20.8888888888889" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1">
+    <row r="1" ht="30" customHeight="1" spans="1:7">
       <c r="A1" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:4">
+      <c r="E1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1" spans="1:7">
       <c r="A2" t="s">
         <v>10</v>
       </c>
-      <c r="B2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
+      <c r="B2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2"/>
+      <c r="G2" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1" spans="1:7">
       <c r="A3" t="s">
         <v>10</v>
       </c>
-      <c r="B3" t="s">
-        <v>5</v>
-      </c>
+      <c r="B3"/>
       <c r="C3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
+        <v>11</v>
+      </c>
+      <c r="D3"/>
+      <c r="E3"/>
+      <c r="F3"/>
+      <c r="G3" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1" spans="1:4">
       <c r="A4" t="s">
         <v>10</v>
       </c>
-      <c r="B4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" t="s">
-        <v>5</v>
-      </c>
-      <c r="D4" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
+      <c r="B4"/>
+      <c r="C4"/>
+      <c r="D4" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1" spans="1:6">
       <c r="A5" t="s">
         <v>10</v>
       </c>
-      <c r="B5" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D5" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
+      <c r="B5"/>
+      <c r="C5"/>
+      <c r="D5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1" spans="1:8">
       <c r="A6" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="7" spans="1:1">
+      <c r="B6"/>
+      <c r="C6"/>
+      <c r="F6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1" spans="1:8">
       <c r="A7" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="8" spans="1:1">
+      <c r="H7" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1" spans="1:8">
       <c r="A8" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="9" spans="1:10">
+      <c r="F8" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1" spans="1:1">
       <c r="A9" t="s">
         <v>10</v>
       </c>
-      <c r="B9"/>
-      <c r="E9" t="s">
-        <v>5</v>
-      </c>
-      <c r="F9" t="s">
-        <v>5</v>
-      </c>
-      <c r="G9" t="s">
-        <v>5</v>
-      </c>
-      <c r="H9" t="s">
-        <v>5</v>
-      </c>
-      <c r="I9" t="s">
-        <v>5</v>
-      </c>
-      <c r="J9" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10">
+    </row>
+    <row r="10" ht="30" customHeight="1" spans="1:1">
       <c r="A10" t="s">
         <v>10</v>
       </c>
-      <c r="B10"/>
-      <c r="E10" t="s">
-        <v>5</v>
-      </c>
-      <c r="F10" t="s">
-        <v>5</v>
-      </c>
-      <c r="G10" t="s">
-        <v>5</v>
-      </c>
-      <c r="H10" t="s">
-        <v>5</v>
-      </c>
-      <c r="I10" t="s">
-        <v>5</v>
-      </c>
-      <c r="J10" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10">
+    </row>
+    <row r="11" ht="30" customHeight="1" spans="1:1">
       <c r="A11" t="s">
         <v>10</v>
       </c>
-      <c r="B11"/>
-      <c r="E11" t="s">
-        <v>5</v>
-      </c>
-      <c r="F11" t="s">
-        <v>5</v>
-      </c>
-      <c r="G11" t="s">
-        <v>5</v>
-      </c>
-      <c r="H11" t="s">
-        <v>5</v>
-      </c>
-      <c r="I11" t="s">
-        <v>5</v>
-      </c>
-      <c r="J11" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10">
+    </row>
+    <row r="12" ht="30" customHeight="1" spans="1:1">
       <c r="A12" t="s">
         <v>10</v>
       </c>
-      <c r="B12"/>
-      <c r="C12"/>
-      <c r="D12"/>
-      <c r="E12" t="s">
-        <v>5</v>
-      </c>
-      <c r="F12" t="s">
-        <v>5</v>
-      </c>
-      <c r="G12" t="s">
-        <v>5</v>
-      </c>
-      <c r="H12" t="s">
-        <v>5</v>
-      </c>
-      <c r="I12" t="s">
-        <v>5</v>
-      </c>
-      <c r="J12" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10">
+    </row>
+    <row r="13" ht="30" customHeight="1" spans="1:1">
       <c r="A13" t="s">
         <v>10</v>
       </c>
-      <c r="B13"/>
-      <c r="C13"/>
-      <c r="D13"/>
-      <c r="E13" t="s">
-        <v>5</v>
-      </c>
-      <c r="F13" t="s">
-        <v>5</v>
-      </c>
-      <c r="G13" t="s">
-        <v>5</v>
-      </c>
-      <c r="H13" t="s">
-        <v>5</v>
-      </c>
-      <c r="I13" t="s">
-        <v>5</v>
-      </c>
-      <c r="J13" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10">
+    </row>
+    <row r="14" ht="30" customHeight="1" spans="1:1">
       <c r="A14" t="s">
         <v>10</v>
       </c>
-      <c r="B14"/>
-      <c r="C14"/>
-      <c r="D14"/>
-      <c r="E14" t="s">
-        <v>5</v>
-      </c>
-      <c r="F14" t="s">
-        <v>5</v>
-      </c>
-      <c r="G14" t="s">
-        <v>5</v>
-      </c>
-      <c r="H14" t="s">
-        <v>5</v>
-      </c>
-      <c r="I14" t="s">
-        <v>5</v>
-      </c>
-      <c r="J14" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10">
+    </row>
+    <row r="15" ht="30" customHeight="1" spans="1:1">
       <c r="A15" t="s">
         <v>10</v>
       </c>
-      <c r="E15" t="s">
-        <v>5</v>
-      </c>
-      <c r="F15" t="s">
-        <v>5</v>
-      </c>
-      <c r="G15" t="s">
-        <v>5</v>
-      </c>
-      <c r="H15" t="s">
-        <v>5</v>
-      </c>
-      <c r="I15" t="s">
-        <v>5</v>
-      </c>
-      <c r="J15" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10">
+    </row>
+    <row r="16" ht="30" customHeight="1" spans="1:1">
       <c r="A16" t="s">
         <v>10</v>
       </c>
-      <c r="E16" t="s">
-        <v>5</v>
-      </c>
-      <c r="F16" t="s">
-        <v>5</v>
-      </c>
-      <c r="G16" t="s">
-        <v>5</v>
-      </c>
-      <c r="H16" t="s">
-        <v>5</v>
-      </c>
-      <c r="I16" t="s">
-        <v>5</v>
-      </c>
-      <c r="J16" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10">
+    </row>
+    <row r="17" ht="30" customHeight="1" spans="1:1">
       <c r="A17" t="s">
         <v>10</v>
       </c>
-      <c r="E17" t="s">
-        <v>5</v>
-      </c>
-      <c r="F17" t="s">
-        <v>5</v>
-      </c>
-      <c r="G17" t="s">
-        <v>5</v>
-      </c>
-      <c r="H17" t="s">
-        <v>5</v>
-      </c>
-      <c r="I17" t="s">
-        <v>5</v>
-      </c>
-      <c r="J17" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10">
+    </row>
+    <row r="18" ht="30" customHeight="1" spans="1:1">
       <c r="A18" t="s">
         <v>10</v>
       </c>
-      <c r="E18" t="s">
-        <v>5</v>
-      </c>
-      <c r="F18" t="s">
-        <v>5</v>
-      </c>
-      <c r="G18" t="s">
-        <v>5</v>
-      </c>
-      <c r="H18" t="s">
-        <v>5</v>
-      </c>
-      <c r="I18" t="s">
-        <v>5</v>
-      </c>
-      <c r="J18" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10">
+    </row>
+    <row r="19" ht="30" customHeight="1" spans="1:1">
       <c r="A19" t="s">
         <v>10</v>
       </c>
-      <c r="E19" t="s">
-        <v>5</v>
-      </c>
-      <c r="F19" t="s">
-        <v>5</v>
-      </c>
-      <c r="G19" t="s">
-        <v>5</v>
-      </c>
-      <c r="H19" t="s">
-        <v>5</v>
-      </c>
-      <c r="I19" t="s">
-        <v>5</v>
-      </c>
-      <c r="J19" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10">
+    </row>
+    <row r="20" ht="30" customHeight="1" spans="1:1">
       <c r="A20" t="s">
         <v>10</v>
       </c>
-      <c r="E20" t="s">
-        <v>5</v>
-      </c>
-      <c r="F20" t="s">
-        <v>5</v>
-      </c>
-      <c r="G20" t="s">
-        <v>5</v>
-      </c>
-      <c r="H20" t="s">
-        <v>5</v>
-      </c>
-      <c r="I20" t="s">
-        <v>5</v>
-      </c>
-      <c r="J20" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10">
+    </row>
+    <row r="21" ht="30" customHeight="1" spans="1:1">
       <c r="A21" t="s">
         <v>10</v>
       </c>
-      <c r="E21" t="s">
-        <v>5</v>
-      </c>
-      <c r="F21" t="s">
-        <v>5</v>
-      </c>
-      <c r="G21" t="s">
-        <v>5</v>
-      </c>
-      <c r="H21" t="s">
-        <v>5</v>
-      </c>
-      <c r="I21" t="s">
-        <v>5</v>
-      </c>
-      <c r="J21" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10">
+    </row>
+    <row r="22" ht="30" customHeight="1" spans="1:1">
       <c r="A22" t="s">
         <v>10</v>
       </c>
-      <c r="E22" t="s">
-        <v>5</v>
-      </c>
-      <c r="F22" t="s">
-        <v>5</v>
-      </c>
-      <c r="G22" t="s">
-        <v>5</v>
-      </c>
-      <c r="H22" t="s">
-        <v>5</v>
-      </c>
-      <c r="I22" t="s">
-        <v>5</v>
-      </c>
-      <c r="J22" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10">
+    </row>
+    <row r="23" ht="30" customHeight="1" spans="1:1">
       <c r="A23" t="s">
         <v>10</v>
       </c>
-      <c r="E23" t="s">
-        <v>5</v>
-      </c>
-      <c r="F23" t="s">
-        <v>5</v>
-      </c>
-      <c r="G23" t="s">
-        <v>5</v>
-      </c>
-      <c r="H23" t="s">
-        <v>5</v>
-      </c>
-      <c r="I23" t="s">
-        <v>5</v>
-      </c>
-      <c r="J23" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10">
+    </row>
+    <row r="24" ht="30" customHeight="1" spans="1:1">
       <c r="A24" t="s">
         <v>10</v>
       </c>
-      <c r="E24" t="s">
-        <v>5</v>
-      </c>
-      <c r="F24" t="s">
-        <v>5</v>
-      </c>
-      <c r="G24" t="s">
-        <v>5</v>
-      </c>
-      <c r="H24" t="s">
-        <v>5</v>
-      </c>
-      <c r="I24" t="s">
-        <v>5</v>
-      </c>
-      <c r="J24" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1">
+    </row>
+    <row r="25" ht="30" customHeight="1" spans="1:1">
       <c r="A25" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="26" spans="1:1">
+    <row r="26" ht="30" customHeight="1" spans="1:1">
       <c r="A26" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="27" spans="1:1">
+    <row r="27" ht="30" customHeight="1" spans="1:1">
       <c r="A27" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="28" spans="1:1">
+    <row r="28" ht="30" customHeight="1" spans="1:1">
       <c r="A28" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="29" spans="1:1">
+    <row r="29" ht="30" customHeight="1" spans="1:1">
       <c r="A29" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="30" spans="1:1">
+    <row r="30" ht="30" customHeight="1" spans="1:1">
       <c r="A30" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="31" spans="1:1">
+    <row r="31" ht="30" customHeight="1" spans="1:1">
       <c r="A31" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="32" spans="1:1">
+    <row r="32" ht="30" customHeight="1" spans="1:1">
       <c r="A32" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="33" spans="1:1">
+    <row r="33" ht="30" customHeight="1" spans="1:1">
       <c r="A33" t="s">
         <v>10</v>
       </c>

--- a/DESIGN.xlsx
+++ b/DESIGN.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="13">
   <si>
     <t>模块类型#朝向</t>
   </si>
@@ -61,6 +61,9 @@
   </si>
   <si>
     <t>PLACEHOLDER</t>
+  </si>
+  <si>
+    <t>###THRUSTER#→</t>
   </si>
   <si>
     <t>JOINT</t>
@@ -1312,7 +1315,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:7">
@@ -1342,7 +1345,7 @@
       </c>
       <c r="B3"/>
       <c r="C3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D3"/>
       <c r="E3"/>
@@ -1412,7 +1415,7 @@
         <v>5</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1" spans="1:1">

--- a/DESIGN.xlsx
+++ b/DESIGN.xlsx
@@ -66,7 +66,7 @@
     <t>###THRUSTER#→</t>
   </si>
   <si>
-    <t>JOINT</t>
+    <t>###JOINT#Vehicle_0#Vehicle_1</t>
   </si>
 </sst>
 </file>
@@ -1344,10 +1344,9 @@
         <v>10</v>
       </c>
       <c r="B3"/>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>12</v>
       </c>
-      <c r="D3"/>
       <c r="E3"/>
       <c r="F3"/>
       <c r="G3" s="1" t="s">

--- a/DESIGN.xlsx
+++ b/DESIGN.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="14">
   <si>
     <t>模块类型#朝向</t>
   </si>
@@ -66,7 +66,10 @@
     <t>###THRUSTER#→</t>
   </si>
   <si>
-    <t>###JOINT#Vehicle_0#Vehicle_1</t>
+    <t>###JBIND#1</t>
+  </si>
+  <si>
+    <t>###JOINT#1</t>
   </si>
 </sst>
 </file>
@@ -1329,12 +1332,11 @@
         <v>5</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F2"/>
       <c r="G2" s="1" t="s">
         <v>5</v>
       </c>
@@ -1343,12 +1345,6 @@
       <c r="A3" t="s">
         <v>10</v>
       </c>
-      <c r="B3"/>
-      <c r="D3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3"/>
-      <c r="F3"/>
       <c r="G3" s="1" t="s">
         <v>5</v>
       </c>
@@ -1357,49 +1353,34 @@
       <c r="A4" t="s">
         <v>10</v>
       </c>
-      <c r="B4"/>
-      <c r="C4"/>
       <c r="D4" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" ht="30" customHeight="1" spans="1:6">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1" spans="1:1">
       <c r="A5" t="s">
         <v>10</v>
       </c>
-      <c r="B5"/>
-      <c r="C5"/>
-      <c r="D5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" ht="30" customHeight="1" spans="1:8">
+    </row>
+    <row r="6" ht="30" customHeight="1" spans="1:4">
       <c r="A6" t="s">
         <v>10</v>
       </c>
-      <c r="B6"/>
-      <c r="C6"/>
-      <c r="F6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" ht="30" customHeight="1" spans="1:8">
+      <c r="D6" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1" spans="1:6">
       <c r="A7" t="s">
         <v>10</v>
       </c>
-      <c r="H7" s="1" t="s">
+      <c r="D7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F7" s="1" t="s">
         <v>5</v>
       </c>
     </row>
@@ -1414,17 +1395,29 @@
         <v>5</v>
       </c>
       <c r="H8" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1" spans="1:8">
+      <c r="A9" t="s">
+        <v>10</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1" spans="1:8">
+      <c r="A10" t="s">
+        <v>10</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H10" s="1" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="9" ht="30" customHeight="1" spans="1:1">
-      <c r="A9" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" ht="30" customHeight="1" spans="1:1">
-      <c r="A10" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1" spans="1:1">

--- a/DESIGN.xlsx
+++ b/DESIGN.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="16">
   <si>
     <t>模块类型#朝向</t>
   </si>
@@ -70,6 +70,12 @@
   </si>
   <si>
     <t>###JOINT#1</t>
+  </si>
+  <si>
+    <t>###JBIND#2</t>
+  </si>
+  <si>
+    <t>###JOINT#2</t>
   </si>
 </sst>
 </file>
@@ -1299,34 +1305,39 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H33"/>
-  <sheetFormatPr defaultColWidth="15.7777777777778" defaultRowHeight="14.4" outlineLevelCol="7"/>
+  <dimension ref="A1:F33"/>
+  <sheetFormatPr defaultColWidth="15.7777777777778" defaultRowHeight="14.4" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="9" width="5.77777777777778" customWidth="1"/>
-    <col min="10" max="11" width="19.7777777777778" customWidth="1"/>
+    <col min="1" max="1" width="13" customWidth="1"/>
+    <col min="2" max="4" width="16.4444444444444" customWidth="1"/>
+    <col min="5" max="6" width="8.66666666666667" customWidth="1"/>
+    <col min="7" max="8" width="5.77777777777778" customWidth="1"/>
+    <col min="9" max="9" width="8.66666666666667" customWidth="1"/>
+    <col min="10" max="10" width="16.4444444444444" customWidth="1"/>
+    <col min="11" max="11" width="8.66666666666667" customWidth="1"/>
     <col min="12" max="13" width="20.8888888888889" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" spans="1:7">
+    <row r="1" ht="30" customHeight="1" spans="1:5">
       <c r="A1" t="s">
         <v>10</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>11</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2" ht="30" customHeight="1" spans="1:7">
+    </row>
+    <row r="2" ht="30" customHeight="1" spans="1:5">
       <c r="A2" t="s">
         <v>10</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>5</v>
@@ -1337,16 +1348,10 @@
       <c r="E2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" ht="30" customHeight="1" spans="1:7">
+    </row>
+    <row r="3" ht="30" customHeight="1" spans="1:1">
       <c r="A3" t="s">
         <v>10</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:4">
@@ -1366,58 +1371,47 @@
       <c r="A6" t="s">
         <v>10</v>
       </c>
+      <c r="B6"/>
+      <c r="C6"/>
       <c r="D6" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1" spans="1:4">
+      <c r="A7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7"/>
+      <c r="C7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" ht="30" customHeight="1" spans="1:6">
-      <c r="A7" t="s">
-        <v>10</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E7" s="1" t="s">
+    <row r="8" ht="30" customHeight="1" spans="1:4">
+      <c r="A8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8"/>
+      <c r="D8" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F7" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" ht="30" customHeight="1" spans="1:8">
-      <c r="A8" t="s">
-        <v>10</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" ht="30" customHeight="1" spans="1:8">
+    </row>
+    <row r="9" ht="30" customHeight="1" spans="1:4">
       <c r="A9" t="s">
         <v>10</v>
       </c>
-      <c r="H9" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" ht="30" customHeight="1" spans="1:8">
+      <c r="D9" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1" spans="1:4">
       <c r="A10" t="s">
         <v>10</v>
       </c>
-      <c r="F10" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H10" s="1" t="s">
-        <v>11</v>
+      <c r="D10" s="1" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1" spans="1:1">
@@ -1425,9 +1419,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" ht="30" customHeight="1" spans="1:1">
+    <row r="12" ht="30" customHeight="1" spans="1:4">
       <c r="A12" t="s">
         <v>10</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1" spans="1:1">
@@ -1435,14 +1432,35 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" ht="30" customHeight="1" spans="1:1">
+    <row r="14" ht="30" customHeight="1" spans="1:5">
       <c r="A14" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="15" ht="30" customHeight="1" spans="1:1">
+      <c r="C14" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1" spans="1:6">
       <c r="A15" t="s">
         <v>10</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1" spans="1:1">

--- a/DESIGN.xlsx
+++ b/DESIGN.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="13">
   <si>
     <t>模块类型#朝向</t>
   </si>
@@ -63,19 +63,10 @@
     <t>PLACEHOLDER</t>
   </si>
   <si>
-    <t>###THRUSTER#→</t>
-  </si>
-  <si>
     <t>###JBIND#1</t>
   </si>
   <si>
     <t>###JOINT#1</t>
-  </si>
-  <si>
-    <t>###JBIND#2</t>
-  </si>
-  <si>
-    <t>###JOINT#2</t>
   </si>
 </sst>
 </file>
@@ -1305,34 +1296,50 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F33"/>
-  <sheetFormatPr defaultColWidth="15.7777777777778" defaultRowHeight="14.4" outlineLevelCol="5"/>
+  <dimension ref="A1:L33"/>
+  <sheetFormatPr defaultColWidth="15.7777777777778" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
-    <col min="2" max="4" width="16.4444444444444" customWidth="1"/>
-    <col min="5" max="6" width="8.66666666666667" customWidth="1"/>
-    <col min="7" max="8" width="5.77777777777778" customWidth="1"/>
-    <col min="9" max="9" width="8.66666666666667" customWidth="1"/>
-    <col min="10" max="10" width="16.4444444444444" customWidth="1"/>
-    <col min="11" max="11" width="8.66666666666667" customWidth="1"/>
-    <col min="12" max="13" width="20.8888888888889" customWidth="1"/>
+    <col min="2" max="4" width="8.66666666666667" customWidth="1"/>
+    <col min="5" max="5" width="11.8888888888889" customWidth="1"/>
+    <col min="6" max="6" width="8.66666666666667" customWidth="1"/>
+    <col min="7" max="7" width="11.8888888888889" customWidth="1"/>
+    <col min="8" max="8" width="5.77777777777778" customWidth="1"/>
+    <col min="9" max="9" width="11.8888888888889" customWidth="1"/>
+    <col min="10" max="12" width="8.66666666666667" customWidth="1"/>
+    <col min="13" max="13" width="20.8888888888889" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" spans="1:5">
+    <row r="1" ht="30" customHeight="1" spans="1:12">
       <c r="A1" t="s">
         <v>10</v>
       </c>
+      <c r="B1" s="1" t="s">
+        <v>5</v>
+      </c>
       <c r="C1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" ht="30" customHeight="1" spans="1:5">
+      <c r="I1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1" spans="1:12">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -1343,23 +1350,59 @@
         <v>5</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" ht="30" customHeight="1" spans="1:1">
+      <c r="I2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1" spans="1:12">
       <c r="A3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="4" ht="30" customHeight="1" spans="1:4">
+      <c r="B3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1" spans="1:1">
       <c r="A4" t="s">
         <v>10</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:1">
@@ -1367,51 +1410,29 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" ht="30" customHeight="1" spans="1:4">
+    <row r="6" ht="30" customHeight="1" spans="1:1">
       <c r="A6" t="s">
         <v>10</v>
       </c>
-      <c r="B6"/>
-      <c r="C6"/>
-      <c r="D6" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" ht="30" customHeight="1" spans="1:4">
+    </row>
+    <row r="7" ht="30" customHeight="1" spans="1:1">
       <c r="A7" t="s">
         <v>10</v>
       </c>
-      <c r="B7"/>
-      <c r="C7" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" ht="30" customHeight="1" spans="1:4">
+    </row>
+    <row r="8" ht="30" customHeight="1" spans="1:1">
       <c r="A8" t="s">
         <v>10</v>
       </c>
-      <c r="B8"/>
-      <c r="D8" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" ht="30" customHeight="1" spans="1:4">
+    </row>
+    <row r="9" ht="30" customHeight="1" spans="1:1">
       <c r="A9" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="10" ht="30" customHeight="1" spans="1:4">
+    </row>
+    <row r="10" ht="30" customHeight="1" spans="1:1">
       <c r="A10" t="s">
         <v>10</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1" spans="1:1">
@@ -1419,12 +1440,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" ht="30" customHeight="1" spans="1:4">
+    <row r="12" ht="30" customHeight="1" spans="1:1">
       <c r="A12" t="s">
         <v>10</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1" spans="1:1">
@@ -1432,35 +1450,14 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" ht="30" customHeight="1" spans="1:5">
+    <row r="14" ht="30" customHeight="1" spans="1:1">
       <c r="A14" t="s">
         <v>10</v>
       </c>
-      <c r="C14" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" ht="30" customHeight="1" spans="1:6">
+    </row>
+    <row r="15" ht="30" customHeight="1" spans="1:1">
       <c r="A15" t="s">
         <v>10</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1" spans="1:1">

--- a/DESIGN.xlsx
+++ b/DESIGN.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="11">
   <si>
     <t>模块类型#朝向</t>
   </si>
@@ -61,12 +61,6 @@
   </si>
   <si>
     <t>PLACEHOLDER</t>
-  </si>
-  <si>
-    <t>###JBIND#1</t>
-  </si>
-  <si>
-    <t>###JOINT#1</t>
   </si>
 </sst>
 </file>
@@ -1296,8 +1290,8 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L33"/>
-  <sheetFormatPr defaultColWidth="15.7777777777778" defaultRowHeight="14.4"/>
+  <dimension ref="A1:H33"/>
+  <sheetFormatPr defaultColWidth="15.7777777777778" defaultRowHeight="14.4" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
     <col min="2" max="4" width="8.66666666666667" customWidth="1"/>
@@ -1310,68 +1304,45 @@
     <col min="13" max="13" width="20.8888888888889" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" spans="1:12">
+    <row r="1" ht="30" customHeight="1" spans="1:8">
       <c r="A1" t="s">
         <v>10</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="1" t="s">
+    </row>
+    <row r="2" ht="30" customHeight="1" spans="1:8">
+      <c r="A2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="C2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2"/>
+      <c r="F2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="L1" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" ht="30" customHeight="1" spans="1:12">
-      <c r="A2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" ht="30" customHeight="1" spans="1:12">
+    </row>
+    <row r="3" ht="30" customHeight="1" spans="1:8">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -1382,21 +1353,15 @@
         <v>5</v>
       </c>
       <c r="D3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="I3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="L3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>5</v>
       </c>
     </row>

--- a/DESIGN.xlsx
+++ b/DESIGN.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="11">
   <si>
     <t>模块类型#朝向</t>
   </si>
@@ -1290,8 +1290,8 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H33"/>
-  <sheetFormatPr defaultColWidth="15.7777777777778" defaultRowHeight="14.4" outlineLevelCol="7"/>
+  <dimension ref="A1:L33"/>
+  <sheetFormatPr defaultColWidth="15.7777777777778" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
     <col min="2" max="4" width="8.66666666666667" customWidth="1"/>
@@ -1304,34 +1304,27 @@
     <col min="13" max="13" width="20.8888888888889" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" spans="1:8">
+    <row r="1" ht="30" customHeight="1" spans="1:5">
       <c r="A1" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1"/>
+      <c r="C1"/>
+      <c r="D1"/>
+      <c r="E1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="F1" s="1" t="s">
+    </row>
+    <row r="2" ht="30" customHeight="1" spans="1:12">
+      <c r="A2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2"/>
+      <c r="C2"/>
+      <c r="D2"/>
+      <c r="E2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" ht="30" customHeight="1" spans="1:8">
-      <c r="A2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2"/>
       <c r="F2" s="1" t="s">
         <v>5</v>
       </c>
@@ -1341,27 +1334,27 @@
       <c r="H2" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" ht="30" customHeight="1" spans="1:8">
+      <c r="I2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1" spans="1:5">
       <c r="A3" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H3" s="1" t="s">
+      <c r="B3"/>
+      <c r="C3"/>
+      <c r="D3"/>
+      <c r="E3" s="1" t="s">
         <v>5</v>
       </c>
     </row>

--- a/DESIGN.xlsx
+++ b/DESIGN.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="11">
   <si>
     <t>模块类型#朝向</t>
   </si>
@@ -1323,7 +1323,7 @@
       <c r="C2"/>
       <c r="D2"/>
       <c r="E2" s="1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>5</v>
@@ -1344,10 +1344,10 @@
         <v>5</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" ht="30" customHeight="1" spans="1:5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1" spans="1:12">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -1357,6 +1357,9 @@
       <c r="E3" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="L3" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:1">
       <c r="A4" t="s">
